--- a/Form-Layout/ImportLayouts/Config/RPT_Import_Map.xlsx
+++ b/Form-Layout/ImportLayouts/Config/RPT_Import_Map.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SBO_Warit\Form-Layout\ImportLayouts\Config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\GitHub\SBO_Seoul\Form-Layout\ImportLayouts\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D87787DE-2E36-46E3-A08B-E61C1993F1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{574C74F8-808E-4F14-A9E2-6561A3BA2FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{014D90F8-196E-40BF-BFE8-06F39FDF4BE1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{014D90F8-196E-40BF-BFE8-06F39FDF4BE1}"/>
   </bookViews>
   <sheets>
     <sheet name="RPT_MAP" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="415">
   <si>
     <t>No</t>
   </si>
@@ -285,27 +285,6 @@
     <t>ใบขอซื้อ</t>
   </si>
   <si>
-    <t>1.Purchase Quotation_ใบเสนอราคาซื้อ.rpt</t>
-  </si>
-  <si>
-    <t>3. Purchasing - AP\2. Purchase Quotation\1.Purchase Quotation_ใบเสนอราคาซื้อ</t>
-  </si>
-  <si>
-    <t>Purchase Quotation</t>
-  </si>
-  <si>
-    <t>OPQT</t>
-  </si>
-  <si>
-    <t>PQT1</t>
-  </si>
-  <si>
-    <t>Purchase Quotation - SDA</t>
-  </si>
-  <si>
-    <t>ใบเสนอราคาซื้อ</t>
-  </si>
-  <si>
     <t>1.Purchase Order_TH_ใบสั่งซื้อ.rpt</t>
   </si>
   <si>
@@ -1062,12 +1041,6 @@
     <t>1.Sale Quotation_ใบเสนอราคาขาย_(Dis) ENG.rpt</t>
   </si>
   <si>
-    <t>1.Retrun_ใบรับคืนสินค้า_ENG (Batch_Serial).rpt</t>
-  </si>
-  <si>
-    <t>Return (B/S) EN - SDA</t>
-  </si>
-  <si>
     <t>Batch/Serial + ภาษาอังกฤษ</t>
   </si>
   <si>
@@ -1191,30 +1164,9 @@
     <t>Batch/Serial + รองรับส่วนลด + ภาษาอังกฤษ</t>
   </si>
   <si>
-    <t>1.Purchase Order_ENG_ใบสั่งซื้อ.rpt</t>
-  </si>
-  <si>
-    <t>Purchase Order EN - SDA</t>
-  </si>
-  <si>
-    <t>1.AP Down Payment_ENG ใบจ่ายเงินมัดจำ.rpt</t>
-  </si>
-  <si>
-    <t>3. Purchasing - AP\6. AP Down Payment Invoice\1.AP Down Payment ใบจ่ายเงินมัดจำ</t>
-  </si>
-  <si>
     <t>AP DP EN - SDA</t>
   </si>
   <si>
-    <t>1.AP Down Payment_ใบจ่ายเงินมัดจำ.rpt</t>
-  </si>
-  <si>
-    <t>AP DP - SDA</t>
-  </si>
-  <si>
-    <t>AP Down Payment_ใบจ่ายเงินมัดจำ</t>
-  </si>
-  <si>
     <t>2.AP Down Payment Invoice_ENG ใบจ่ายเงินมัดจำใบกำกับภาษี.rpt</t>
   </si>
   <si>
@@ -1312,6 +1264,24 @@
   </si>
   <si>
     <t>Inventory Transfer_ใบโอนสินค้า</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>2.Purchase Order_TH_ใบสั่งซื้อ(BPcatolog).rpt</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>Purchase Order (BP Catalog) - SDA</t>
+  </si>
+  <si>
+    <t>ใบสั่งซื้อ (BP Catalog No.)</t>
   </si>
 </sst>
 </file>
@@ -1413,7 +1383,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1445,6 +1415,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1779,21 +1750,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F62795C-81CC-4DF6-8643-8C6776741771}">
-  <dimension ref="A1:K76"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K72"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.69921875" customWidth="1"/>
-    <col min="2" max="2" width="14.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="55.69921875" customWidth="1"/>
-    <col min="5" max="5" width="22.69921875" customWidth="1"/>
-    <col min="6" max="8" width="12.69921875" customWidth="1"/>
-    <col min="9" max="9" width="14.69921875" customWidth="1"/>
-    <col min="10" max="10" width="28.69921875" customWidth="1"/>
-    <col min="11" max="11" width="22.69921875" customWidth="1"/>
+    <col min="1" max="1" width="5.75" customWidth="1"/>
+    <col min="2" max="2" width="14.75" customWidth="1"/>
+    <col min="3" max="3" width="45.75" customWidth="1"/>
+    <col min="4" max="4" width="55.75" customWidth="1"/>
+    <col min="5" max="5" width="22.75" customWidth="1"/>
+    <col min="6" max="8" width="12.75" customWidth="1"/>
+    <col min="9" max="9" width="14.75" customWidth="1"/>
+    <col min="10" max="10" width="28.75" customWidth="1"/>
+    <col min="11" max="11" width="22.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1828,7 +1799,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="11">
         <v>1</v>
       </c>
@@ -1863,7 +1834,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>4</v>
       </c>
@@ -1898,7 +1869,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4" s="11">
         <v>5</v>
       </c>
@@ -1906,7 +1877,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>24</v>
@@ -1933,7 +1904,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>6</v>
       </c>
@@ -1941,7 +1912,7 @@
         <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>29</v>
@@ -1968,7 +1939,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>8</v>
       </c>
@@ -2003,7 +1974,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
         <v>9</v>
       </c>
@@ -2038,7 +2009,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>10</v>
       </c>
@@ -2046,7 +2017,7 @@
         <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>44</v>
@@ -2073,7 +2044,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <v>11</v>
       </c>
@@ -2108,7 +2079,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>12</v>
       </c>
@@ -2143,7 +2114,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>13</v>
       </c>
@@ -2178,7 +2149,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" s="11">
         <v>14</v>
       </c>
@@ -2186,7 +2157,7 @@
         <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>71</v>
@@ -2213,7 +2184,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>15</v>
       </c>
@@ -2248,202 +2219,202 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A14" s="12">
-        <v>16</v>
-      </c>
-      <c r="B14" s="3" t="s">
+    <row r="14" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="11">
+        <v>17</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="H14" s="3">
-        <v>540000405</v>
-      </c>
-      <c r="I14" s="3">
-        <v>540000405</v>
-      </c>
-      <c r="J14" s="3" t="s">
+      <c r="H14" s="4">
+        <v>22</v>
+      </c>
+      <c r="I14" s="4">
+        <v>142</v>
+      </c>
+      <c r="J14" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="K14" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A15" s="11">
-        <v>17</v>
-      </c>
-      <c r="B15" s="4" t="s">
+    <row r="15" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="12">
+        <v>18</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="3">
+        <v>20</v>
+      </c>
+      <c r="I15" s="3">
+        <v>143</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A16" s="12">
+        <v>19</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H16" s="4">
+        <v>21</v>
+      </c>
+      <c r="I16" s="4">
+        <v>144</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A17" s="11">
+        <v>20</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H17" s="3">
+        <v>204</v>
+      </c>
+      <c r="I17" s="3">
+        <v>65301</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A18" s="12">
+        <v>21</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="H18" s="4">
+        <v>18</v>
+      </c>
+      <c r="I18" s="4">
+        <v>141</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A19" s="12">
         <v>22</v>
-      </c>
-      <c r="I15" s="4">
-        <v>142</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A16" s="12">
-        <v>18</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="H16" s="3">
-        <v>20</v>
-      </c>
-      <c r="I16" s="3">
-        <v>143</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A17" s="12">
-        <v>19</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="H17" s="4">
-        <v>21</v>
-      </c>
-      <c r="I17" s="4">
-        <v>144</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A18" s="11">
-        <v>20</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="H18" s="3">
-        <v>204</v>
-      </c>
-      <c r="I18" s="3">
-        <v>65301</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A19" s="12">
-        <v>21</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>74</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H19" s="4">
         <v>18</v>
@@ -2452,899 +2423,899 @@
         <v>141</v>
       </c>
       <c r="J19" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" s="11">
+        <v>23</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="K19" s="4" t="s">
+      <c r="F20" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="H20" s="3">
+        <v>18</v>
+      </c>
+      <c r="I20" s="3">
+        <v>141</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A20" s="12">
-        <v>22</v>
-      </c>
-      <c r="B20" s="4" t="s">
+      <c r="K20" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A21" s="12">
+        <v>24</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C21" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="H20" s="4">
-        <v>18</v>
-      </c>
-      <c r="I20" s="4">
+      <c r="D21" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="H21" s="4">
+        <v>19</v>
+      </c>
+      <c r="I21" s="4">
+        <v>181</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A22" s="12">
+        <v>25</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="H22" s="3">
+        <v>69</v>
+      </c>
+      <c r="I22" s="3">
+        <v>992</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A23" s="11">
+        <v>26</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="J20" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="11">
-        <v>23</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H21" s="3">
-        <v>18</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="F23" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H23" s="4">
+        <v>24</v>
+      </c>
+      <c r="I23" s="4">
+        <v>170</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A24" s="12">
+        <v>27</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="12">
+      <c r="F24" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="H24" s="3">
         <v>24</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="H22" s="4">
+      <c r="I24" s="3">
+        <v>170</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A25" s="12">
+        <v>28</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="H25" s="4">
+        <v>46</v>
+      </c>
+      <c r="I25" s="4">
+        <v>171</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A26" s="11">
+        <v>29</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="H26" s="3">
+        <v>59</v>
+      </c>
+      <c r="I26" s="3">
+        <v>720</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A27" s="12">
+        <v>30</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="H27" s="4">
+        <v>60</v>
+      </c>
+      <c r="I27" s="4">
+        <v>721</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A28" s="12">
+        <v>31</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="H28" s="3">
+        <v>1250000001</v>
+      </c>
+      <c r="I28" s="3">
+        <v>1250000001</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A29" s="11">
+        <v>32</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="H29" s="4">
+        <v>67</v>
+      </c>
+      <c r="I29" s="4">
+        <v>940</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A30" s="12">
+        <v>33</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="H30" s="3">
+        <v>1470000065</v>
+      </c>
+      <c r="I30" s="3">
+        <v>1470000065</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A31" s="12">
+        <v>34</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="H31" s="4">
+        <v>1470000065</v>
+      </c>
+      <c r="I31" s="4">
+        <v>1470000065</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A32" s="11">
+        <v>35</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="H32" s="3">
+        <v>162</v>
+      </c>
+      <c r="I32" s="3">
+        <v>184</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A33" s="12">
+        <v>36</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="H33" s="4">
+        <v>162</v>
+      </c>
+      <c r="I33" s="4">
+        <v>184</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" s="12">
+        <v>37</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="H34" s="3">
+        <v>202</v>
+      </c>
+      <c r="I34" s="3">
+        <v>65209</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A35" s="11">
+        <v>38</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="H35" s="4">
+        <v>59</v>
+      </c>
+      <c r="I35" s="4">
+        <v>720</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A36" s="12">
+        <v>39</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="H36" s="3">
+        <v>59</v>
+      </c>
+      <c r="I36" s="3">
+        <v>720</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A37" s="12">
+        <v>40</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="H37" s="4">
+        <v>60</v>
+      </c>
+      <c r="I37" s="4">
+        <v>721</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A38" s="11">
+        <v>41</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="H38" s="3">
+        <v>60</v>
+      </c>
+      <c r="I38" s="3">
+        <v>721</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A39" s="12">
+        <v>42</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A40" s="12">
+        <v>43</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41" s="11">
+        <v>44</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" s="12">
+        <v>45</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>49</v>
+      </c>
+      <c r="B43" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="4">
-        <v>181</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A23" s="12">
-        <v>25</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="H23" s="3">
-        <v>69</v>
-      </c>
-      <c r="I23" s="3">
-        <v>992</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A24" s="11">
-        <v>26</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="H24" s="4">
-        <v>24</v>
-      </c>
-      <c r="I24" s="4">
-        <v>170</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A25" s="12">
-        <v>27</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="H25" s="3">
-        <v>24</v>
-      </c>
-      <c r="I25" s="3">
-        <v>170</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A26" s="12">
-        <v>28</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="H26" s="4">
-        <v>46</v>
-      </c>
-      <c r="I26" s="4">
-        <v>171</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A27" s="11">
-        <v>29</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="H27" s="3">
-        <v>59</v>
-      </c>
-      <c r="I27" s="3">
-        <v>720</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A28" s="12">
-        <v>30</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="H28" s="4">
-        <v>60</v>
-      </c>
-      <c r="I28" s="4">
-        <v>721</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A29" s="12">
-        <v>31</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="H29" s="3">
-        <v>1250000001</v>
-      </c>
-      <c r="I29" s="3">
-        <v>1250000001</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A30" s="11">
-        <v>32</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>422</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="H30" s="4">
-        <v>67</v>
-      </c>
-      <c r="I30" s="4">
-        <v>940</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A31" s="12">
-        <v>33</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="H31" s="3">
-        <v>1470000065</v>
-      </c>
-      <c r="I31" s="3">
-        <v>1470000065</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A32" s="12">
-        <v>34</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="H32" s="4">
-        <v>1470000065</v>
-      </c>
-      <c r="I32" s="4">
-        <v>1470000065</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A33" s="11">
-        <v>35</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D33" s="3" t="s">
+      <c r="C43" t="s">
+        <v>335</v>
+      </c>
+      <c r="D43" t="s">
+        <v>50</v>
+      </c>
+      <c r="E43" t="s">
+        <v>51</v>
+      </c>
+      <c r="F43" t="s">
+        <v>52</v>
+      </c>
+      <c r="G43" t="s">
+        <v>53</v>
+      </c>
+      <c r="H43">
         <v>203</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="H33" s="3">
-        <v>162</v>
-      </c>
-      <c r="I33" s="3">
-        <v>184</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A34" s="12">
-        <v>36</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="H34" s="4">
-        <v>162</v>
-      </c>
-      <c r="I34" s="4">
-        <v>184</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="12">
-        <v>37</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="H35" s="3">
-        <v>202</v>
-      </c>
-      <c r="I35" s="3">
-        <v>65209</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A36" s="11">
-        <v>38</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="H36" s="4">
-        <v>59</v>
-      </c>
-      <c r="I36" s="4">
-        <v>720</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="K36" s="4" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A37" s="12">
-        <v>39</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="H37" s="3">
-        <v>59</v>
-      </c>
-      <c r="I37" s="3">
-        <v>720</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A38" s="12">
-        <v>40</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="H38" s="4">
-        <v>60</v>
-      </c>
-      <c r="I38" s="4">
-        <v>721</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="K38" s="4" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A39" s="11">
-        <v>41</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="H39" s="3">
-        <v>60</v>
-      </c>
-      <c r="I39" s="3">
-        <v>721</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="12">
-        <v>42</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="J40" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="K40" s="4" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="12">
+      <c r="I43">
+        <v>65300</v>
+      </c>
+      <c r="J43" t="s">
+        <v>336</v>
+      </c>
+      <c r="K43" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="11">
-        <v>44</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="K42" s="4" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="12">
-        <v>45</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B44" t="s">
         <v>19</v>
       </c>
       <c r="C44" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D44" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E44" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F44" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G44" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="H44">
-        <v>16</v>
+        <v>203</v>
       </c>
       <c r="I44">
-        <v>141</v>
+        <v>65300</v>
       </c>
       <c r="J44" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="K44" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B45" t="s">
         <v>19</v>
       </c>
       <c r="C45" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="D45" t="s">
-        <v>50</v>
+        <v>338</v>
       </c>
       <c r="E45" t="s">
         <v>51</v>
@@ -3362,24 +3333,24 @@
         <v>65300</v>
       </c>
       <c r="J45" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="K45" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B46" t="s">
         <v>19</v>
       </c>
       <c r="C46" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D46" t="s">
-        <v>57</v>
+        <v>338</v>
       </c>
       <c r="E46" t="s">
         <v>51</v>
@@ -3397,94 +3368,94 @@
         <v>65300</v>
       </c>
       <c r="J46" t="s">
-        <v>345</v>
+        <v>54</v>
       </c>
       <c r="K46" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B47" t="s">
         <v>19</v>
       </c>
       <c r="C47" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="D47" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E47" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F47" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G47" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H47">
-        <v>203</v>
+        <v>13</v>
       </c>
       <c r="I47">
-        <v>65300</v>
+        <v>133</v>
       </c>
       <c r="J47" t="s">
+        <v>344</v>
+      </c>
+      <c r="K47" t="s">
         <v>345</v>
       </c>
-      <c r="K47" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B48" t="s">
         <v>19</v>
       </c>
       <c r="C48" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D48" t="s">
+        <v>343</v>
+      </c>
+      <c r="E48" t="s">
+        <v>60</v>
+      </c>
+      <c r="F48" t="s">
+        <v>61</v>
+      </c>
+      <c r="G48" t="s">
+        <v>62</v>
+      </c>
+      <c r="H48">
+        <v>13</v>
+      </c>
+      <c r="I48">
+        <v>133</v>
+      </c>
+      <c r="J48" t="s">
         <v>347</v>
       </c>
-      <c r="E48" t="s">
-        <v>51</v>
-      </c>
-      <c r="F48" t="s">
-        <v>52</v>
-      </c>
-      <c r="G48" t="s">
-        <v>53</v>
-      </c>
-      <c r="H48">
-        <v>203</v>
-      </c>
-      <c r="I48">
-        <v>65300</v>
-      </c>
-      <c r="J48" t="s">
-        <v>54</v>
-      </c>
       <c r="K48" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B49" t="s">
         <v>19</v>
       </c>
       <c r="C49" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D49" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E49" t="s">
         <v>60</v>
@@ -3502,24 +3473,24 @@
         <v>133</v>
       </c>
       <c r="J49" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="K49" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B50" t="s">
         <v>19</v>
       </c>
       <c r="C50" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="D50" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E50" t="s">
         <v>60</v>
@@ -3537,24 +3508,24 @@
         <v>133</v>
       </c>
       <c r="J50" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="K50" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B51" t="s">
         <v>19</v>
       </c>
       <c r="C51" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="D51" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="E51" t="s">
         <v>60</v>
@@ -3572,24 +3543,24 @@
         <v>133</v>
       </c>
       <c r="J51" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="K51" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B52" t="s">
         <v>19</v>
       </c>
       <c r="C52" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="D52" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="E52" t="s">
         <v>60</v>
@@ -3607,94 +3578,94 @@
         <v>133</v>
       </c>
       <c r="J52" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="K52" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B53" t="s">
         <v>19</v>
       </c>
       <c r="C53" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="D53" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="E53" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F53" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G53" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H53">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I53">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="J53" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K53" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B54" t="s">
         <v>19</v>
       </c>
       <c r="C54" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D54" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="E54" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F54" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G54" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H54">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I54">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="J54" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="K54" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B55" t="s">
         <v>19</v>
       </c>
       <c r="C55" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D55" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E55" t="s">
         <v>64</v>
@@ -3712,24 +3683,24 @@
         <v>179</v>
       </c>
       <c r="J55" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="K55" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B56" t="s">
         <v>19</v>
       </c>
       <c r="C56" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D56" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E56" t="s">
         <v>64</v>
@@ -3747,24 +3718,24 @@
         <v>179</v>
       </c>
       <c r="J56" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="K56" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B57" t="s">
         <v>19</v>
       </c>
       <c r="C57" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D57" t="s">
-        <v>371</v>
+        <v>68</v>
       </c>
       <c r="E57" t="s">
         <v>64</v>
@@ -3782,24 +3753,24 @@
         <v>179</v>
       </c>
       <c r="J57" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="K57" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B58" t="s">
         <v>19</v>
       </c>
       <c r="C58" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D58" t="s">
-        <v>371</v>
+        <v>71</v>
       </c>
       <c r="E58" t="s">
         <v>64</v>
@@ -3817,214 +3788,214 @@
         <v>179</v>
       </c>
       <c r="J58" t="s">
+        <v>373</v>
+      </c>
+      <c r="K58" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>78</v>
+      </c>
+      <c r="B59" t="s">
+        <v>74</v>
+      </c>
+      <c r="C59" t="s">
+        <v>376</v>
+      </c>
+      <c r="D59" t="s">
+        <v>107</v>
+      </c>
+      <c r="E59" t="s">
+        <v>103</v>
+      </c>
+      <c r="F59" t="s">
+        <v>104</v>
+      </c>
+      <c r="G59" t="s">
+        <v>105</v>
+      </c>
+      <c r="H59">
+        <v>204</v>
+      </c>
+      <c r="I59">
+        <v>65301</v>
+      </c>
+      <c r="J59" t="s">
         <v>375</v>
       </c>
-      <c r="K58" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>73</v>
-      </c>
-      <c r="B59" t="s">
-        <v>19</v>
-      </c>
-      <c r="C59" t="s">
+      <c r="K59" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>79</v>
+      </c>
+      <c r="B60" t="s">
+        <v>74</v>
+      </c>
+      <c r="C60" t="s">
         <v>377</v>
       </c>
-      <c r="D59" t="s">
-        <v>68</v>
-      </c>
-      <c r="E59" t="s">
-        <v>64</v>
-      </c>
-      <c r="F59" t="s">
-        <v>65</v>
-      </c>
-      <c r="G59" t="s">
-        <v>66</v>
-      </c>
-      <c r="H59">
-        <v>14</v>
-      </c>
-      <c r="I59">
-        <v>179</v>
-      </c>
-      <c r="J59" t="s">
+      <c r="D60" t="s">
         <v>378</v>
       </c>
-      <c r="K59" t="s">
+      <c r="E60" t="s">
+        <v>110</v>
+      </c>
+      <c r="F60" t="s">
+        <v>111</v>
+      </c>
+      <c r="G60" t="s">
+        <v>112</v>
+      </c>
+      <c r="H60">
+        <v>18</v>
+      </c>
+      <c r="I60">
+        <v>141</v>
+      </c>
+      <c r="J60" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>74</v>
-      </c>
-      <c r="B60" t="s">
-        <v>19</v>
-      </c>
-      <c r="C60" t="s">
-        <v>381</v>
-      </c>
-      <c r="D60" t="s">
-        <v>71</v>
-      </c>
-      <c r="E60" t="s">
-        <v>64</v>
-      </c>
-      <c r="F60" t="s">
-        <v>65</v>
-      </c>
-      <c r="G60" t="s">
-        <v>66</v>
-      </c>
-      <c r="H60">
-        <v>14</v>
-      </c>
-      <c r="I60">
-        <v>179</v>
-      </c>
-      <c r="J60" t="s">
-        <v>382</v>
-      </c>
       <c r="K60" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B61" t="s">
         <v>74</v>
       </c>
       <c r="C61" t="s">
+        <v>381</v>
+      </c>
+      <c r="D61" t="s">
+        <v>382</v>
+      </c>
+      <c r="E61" t="s">
+        <v>110</v>
+      </c>
+      <c r="F61" t="s">
+        <v>111</v>
+      </c>
+      <c r="G61" t="s">
+        <v>112</v>
+      </c>
+      <c r="H61">
+        <v>18</v>
+      </c>
+      <c r="I61">
+        <v>141</v>
+      </c>
+      <c r="J61" t="s">
+        <v>383</v>
+      </c>
+      <c r="K61" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>81</v>
+      </c>
+      <c r="B62" t="s">
+        <v>138</v>
+      </c>
+      <c r="C62" t="s">
         <v>384</v>
       </c>
-      <c r="D61" t="s">
-        <v>90</v>
-      </c>
-      <c r="E61" t="s">
-        <v>91</v>
-      </c>
-      <c r="F61" t="s">
-        <v>92</v>
-      </c>
-      <c r="G61" t="s">
-        <v>93</v>
-      </c>
-      <c r="H61">
-        <v>22</v>
-      </c>
-      <c r="I61">
+      <c r="D62" t="s">
+        <v>140</v>
+      </c>
+      <c r="E62" t="s">
+        <v>141</v>
+      </c>
+      <c r="F62" t="s">
         <v>142</v>
       </c>
-      <c r="J61" t="s">
+      <c r="G62" t="s">
+        <v>143</v>
+      </c>
+      <c r="H62">
+        <v>24</v>
+      </c>
+      <c r="I62">
+        <v>170</v>
+      </c>
+      <c r="J62" t="s">
         <v>385</v>
-      </c>
-      <c r="K61" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>76</v>
-      </c>
-      <c r="B62" t="s">
-        <v>74</v>
-      </c>
-      <c r="C62" t="s">
-        <v>386</v>
-      </c>
-      <c r="D62" t="s">
-        <v>387</v>
-      </c>
-      <c r="E62" t="s">
-        <v>110</v>
-      </c>
-      <c r="F62" t="s">
-        <v>111</v>
-      </c>
-      <c r="G62" t="s">
-        <v>112</v>
-      </c>
-      <c r="H62">
-        <v>204</v>
-      </c>
-      <c r="I62">
-        <v>65301</v>
-      </c>
-      <c r="J62" t="s">
-        <v>388</v>
       </c>
       <c r="K62" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B63" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="C63" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D63" t="s">
+        <v>147</v>
+      </c>
+      <c r="E63" t="s">
+        <v>141</v>
+      </c>
+      <c r="F63" t="s">
+        <v>142</v>
+      </c>
+      <c r="G63" t="s">
+        <v>143</v>
+      </c>
+      <c r="H63">
+        <v>24</v>
+      </c>
+      <c r="I63">
+        <v>170</v>
+      </c>
+      <c r="J63" t="s">
+        <v>385</v>
+      </c>
+      <c r="K63" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>83</v>
+      </c>
+      <c r="B64" t="s">
+        <v>138</v>
+      </c>
+      <c r="C64" t="s">
         <v>387</v>
       </c>
-      <c r="E63" t="s">
-        <v>110</v>
-      </c>
-      <c r="F63" t="s">
-        <v>111</v>
-      </c>
-      <c r="G63" t="s">
-        <v>112</v>
-      </c>
-      <c r="H63">
-        <v>204</v>
-      </c>
-      <c r="I63">
-        <v>65301</v>
-      </c>
-      <c r="J63" t="s">
-        <v>390</v>
-      </c>
-      <c r="K63" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>78</v>
-      </c>
-      <c r="B64" t="s">
-        <v>74</v>
-      </c>
-      <c r="C64" t="s">
-        <v>392</v>
-      </c>
       <c r="D64" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="E64" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="F64" t="s">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="G64" t="s">
-        <v>112</v>
+        <v>153</v>
       </c>
       <c r="H64">
-        <v>204</v>
+        <v>46</v>
       </c>
       <c r="I64">
-        <v>65301</v>
+        <v>171</v>
       </c>
       <c r="J64" t="s">
         <v>388</v>
@@ -4033,193 +4004,193 @@
         <v>43</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B65" t="s">
-        <v>74</v>
+        <v>156</v>
       </c>
       <c r="C65" t="s">
+        <v>389</v>
+      </c>
+      <c r="D65" t="s">
+        <v>390</v>
+      </c>
+      <c r="E65" t="s">
+        <v>159</v>
+      </c>
+      <c r="F65" t="s">
+        <v>160</v>
+      </c>
+      <c r="G65" t="s">
+        <v>161</v>
+      </c>
+      <c r="H65">
+        <v>59</v>
+      </c>
+      <c r="I65">
+        <v>720</v>
+      </c>
+      <c r="J65" t="s">
+        <v>391</v>
+      </c>
+      <c r="K65" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>85</v>
+      </c>
+      <c r="B66" t="s">
+        <v>156</v>
+      </c>
+      <c r="C66" t="s">
+        <v>392</v>
+      </c>
+      <c r="D66" t="s">
+        <v>390</v>
+      </c>
+      <c r="E66" t="s">
+        <v>159</v>
+      </c>
+      <c r="F66" t="s">
+        <v>160</v>
+      </c>
+      <c r="G66" t="s">
+        <v>161</v>
+      </c>
+      <c r="H66">
+        <v>59</v>
+      </c>
+      <c r="I66">
+        <v>720</v>
+      </c>
+      <c r="J66" t="s">
         <v>393</v>
       </c>
-      <c r="D65" t="s">
+      <c r="K66" t="s">
         <v>394</v>
       </c>
-      <c r="E65" t="s">
-        <v>117</v>
-      </c>
-      <c r="F65" t="s">
-        <v>118</v>
-      </c>
-      <c r="G65" t="s">
-        <v>119</v>
-      </c>
-      <c r="H65">
-        <v>18</v>
-      </c>
-      <c r="I65">
-        <v>141</v>
-      </c>
-      <c r="J65" t="s">
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>86</v>
+      </c>
+      <c r="B67" t="s">
+        <v>156</v>
+      </c>
+      <c r="C67" t="s">
         <v>395</v>
       </c>
-      <c r="K65" t="s">
+      <c r="D67" t="s">
+        <v>158</v>
+      </c>
+      <c r="E67" t="s">
+        <v>159</v>
+      </c>
+      <c r="F67" t="s">
+        <v>160</v>
+      </c>
+      <c r="G67" t="s">
+        <v>161</v>
+      </c>
+      <c r="H67">
+        <v>59</v>
+      </c>
+      <c r="I67">
+        <v>720</v>
+      </c>
+      <c r="J67" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>80</v>
-      </c>
-      <c r="B66" t="s">
-        <v>74</v>
-      </c>
-      <c r="C66" t="s">
+      <c r="K67" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>87</v>
+      </c>
+      <c r="B68" t="s">
+        <v>156</v>
+      </c>
+      <c r="C68" t="s">
         <v>397</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D68" t="s">
         <v>398</v>
       </c>
-      <c r="E66" t="s">
-        <v>117</v>
-      </c>
-      <c r="F66" t="s">
-        <v>118</v>
-      </c>
-      <c r="G66" t="s">
-        <v>119</v>
-      </c>
-      <c r="H66">
-        <v>18</v>
-      </c>
-      <c r="I66">
-        <v>141</v>
-      </c>
-      <c r="J66" t="s">
+      <c r="E68" t="s">
+        <v>166</v>
+      </c>
+      <c r="F68" t="s">
+        <v>167</v>
+      </c>
+      <c r="G68" t="s">
+        <v>168</v>
+      </c>
+      <c r="H68">
+        <v>60</v>
+      </c>
+      <c r="I68">
+        <v>721</v>
+      </c>
+      <c r="J68" t="s">
         <v>399</v>
-      </c>
-      <c r="K66" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>81</v>
-      </c>
-      <c r="B67" t="s">
-        <v>145</v>
-      </c>
-      <c r="C67" t="s">
-        <v>400</v>
-      </c>
-      <c r="D67" t="s">
-        <v>147</v>
-      </c>
-      <c r="E67" t="s">
-        <v>148</v>
-      </c>
-      <c r="F67" t="s">
-        <v>149</v>
-      </c>
-      <c r="G67" t="s">
-        <v>150</v>
-      </c>
-      <c r="H67">
-        <v>24</v>
-      </c>
-      <c r="I67">
-        <v>170</v>
-      </c>
-      <c r="J67" t="s">
-        <v>401</v>
-      </c>
-      <c r="K67" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>82</v>
-      </c>
-      <c r="B68" t="s">
-        <v>145</v>
-      </c>
-      <c r="C68" t="s">
-        <v>402</v>
-      </c>
-      <c r="D68" t="s">
-        <v>154</v>
-      </c>
-      <c r="E68" t="s">
-        <v>148</v>
-      </c>
-      <c r="F68" t="s">
-        <v>149</v>
-      </c>
-      <c r="G68" t="s">
-        <v>150</v>
-      </c>
-      <c r="H68">
-        <v>24</v>
-      </c>
-      <c r="I68">
-        <v>170</v>
-      </c>
-      <c r="J68" t="s">
-        <v>401</v>
       </c>
       <c r="K68" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B69" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C69" t="s">
+        <v>400</v>
+      </c>
+      <c r="D69" t="s">
+        <v>398</v>
+      </c>
+      <c r="E69" t="s">
+        <v>166</v>
+      </c>
+      <c r="F69" t="s">
+        <v>167</v>
+      </c>
+      <c r="G69" t="s">
+        <v>168</v>
+      </c>
+      <c r="H69">
+        <v>60</v>
+      </c>
+      <c r="I69">
+        <v>721</v>
+      </c>
+      <c r="J69" t="s">
+        <v>401</v>
+      </c>
+      <c r="K69" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>89</v>
+      </c>
+      <c r="B70" t="s">
+        <v>156</v>
+      </c>
+      <c r="C70" t="s">
         <v>403</v>
       </c>
-      <c r="D69" t="s">
-        <v>157</v>
-      </c>
-      <c r="E69" t="s">
-        <v>158</v>
-      </c>
-      <c r="F69" t="s">
-        <v>159</v>
-      </c>
-      <c r="G69" t="s">
-        <v>160</v>
-      </c>
-      <c r="H69">
-        <v>46</v>
-      </c>
-      <c r="I69">
-        <v>171</v>
-      </c>
-      <c r="J69" t="s">
-        <v>404</v>
-      </c>
-      <c r="K69" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>84</v>
-      </c>
-      <c r="B70" t="s">
-        <v>163</v>
-      </c>
-      <c r="C70" t="s">
-        <v>405</v>
-      </c>
       <c r="D70" t="s">
-        <v>406</v>
+        <v>165</v>
       </c>
       <c r="E70" t="s">
         <v>166</v>
@@ -4231,226 +4202,86 @@
         <v>168</v>
       </c>
       <c r="H70">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I70">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="J70" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="K70" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B71" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C71" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D71" t="s">
         <v>406</v>
       </c>
       <c r="E71" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="F71" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="G71" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H71">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="I71">
-        <v>720</v>
+        <v>940</v>
       </c>
       <c r="J71" t="s">
+        <v>407</v>
+      </c>
+      <c r="K71" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A72" s="13" t="s">
         <v>409</v>
       </c>
-      <c r="K71" t="s">
+      <c r="B72" t="s">
+        <v>74</v>
+      </c>
+      <c r="C72" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A72">
+      <c r="D72" t="s">
+        <v>83</v>
+      </c>
+      <c r="E72" t="s">
+        <v>84</v>
+      </c>
+      <c r="F72" t="s">
+        <v>85</v>
+      </c>
+      <c r="G72" t="s">
         <v>86</v>
       </c>
-      <c r="B72" t="s">
-        <v>163</v>
-      </c>
-      <c r="C72" t="s">
+      <c r="H72" s="13" t="s">
         <v>411</v>
       </c>
-      <c r="D72" t="s">
-        <v>165</v>
-      </c>
-      <c r="E72" t="s">
-        <v>166</v>
-      </c>
-      <c r="F72" t="s">
-        <v>167</v>
-      </c>
-      <c r="G72" t="s">
-        <v>168</v>
-      </c>
-      <c r="H72">
-        <v>59</v>
-      </c>
-      <c r="I72">
-        <v>720</v>
+      <c r="I72" s="13" t="s">
+        <v>412</v>
       </c>
       <c r="J72" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K72" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>87</v>
-      </c>
-      <c r="B73" t="s">
-        <v>163</v>
-      </c>
-      <c r="C73" t="s">
-        <v>413</v>
-      </c>
-      <c r="D73" t="s">
         <v>414</v>
-      </c>
-      <c r="E73" t="s">
-        <v>173</v>
-      </c>
-      <c r="F73" t="s">
-        <v>174</v>
-      </c>
-      <c r="G73" t="s">
-        <v>175</v>
-      </c>
-      <c r="H73">
-        <v>60</v>
-      </c>
-      <c r="I73">
-        <v>721</v>
-      </c>
-      <c r="J73" t="s">
-        <v>415</v>
-      </c>
-      <c r="K73" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>88</v>
-      </c>
-      <c r="B74" t="s">
-        <v>163</v>
-      </c>
-      <c r="C74" t="s">
-        <v>416</v>
-      </c>
-      <c r="D74" t="s">
-        <v>414</v>
-      </c>
-      <c r="E74" t="s">
-        <v>173</v>
-      </c>
-      <c r="F74" t="s">
-        <v>174</v>
-      </c>
-      <c r="G74" t="s">
-        <v>175</v>
-      </c>
-      <c r="H74">
-        <v>60</v>
-      </c>
-      <c r="I74">
-        <v>721</v>
-      </c>
-      <c r="J74" t="s">
-        <v>417</v>
-      </c>
-      <c r="K74" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>89</v>
-      </c>
-      <c r="B75" t="s">
-        <v>163</v>
-      </c>
-      <c r="C75" t="s">
-        <v>419</v>
-      </c>
-      <c r="D75" t="s">
-        <v>172</v>
-      </c>
-      <c r="E75" t="s">
-        <v>173</v>
-      </c>
-      <c r="F75" t="s">
-        <v>174</v>
-      </c>
-      <c r="G75" t="s">
-        <v>175</v>
-      </c>
-      <c r="H75">
-        <v>60</v>
-      </c>
-      <c r="I75">
-        <v>721</v>
-      </c>
-      <c r="J75" t="s">
-        <v>420</v>
-      </c>
-      <c r="K75" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>90</v>
-      </c>
-      <c r="B76" t="s">
-        <v>163</v>
-      </c>
-      <c r="C76" t="s">
-        <v>421</v>
-      </c>
-      <c r="D76" t="s">
-        <v>422</v>
-      </c>
-      <c r="E76" t="s">
-        <v>186</v>
-      </c>
-      <c r="F76" t="s">
-        <v>187</v>
-      </c>
-      <c r="G76" t="s">
-        <v>188</v>
-      </c>
-      <c r="H76">
-        <v>67</v>
-      </c>
-      <c r="I76">
-        <v>940</v>
-      </c>
-      <c r="J76" t="s">
-        <v>423</v>
-      </c>
-      <c r="K76" t="s">
-        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -4461,390 +4292,390 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F598BE85-BEA9-4F93-8400-E7BAEF1B0041}">
   <dimension ref="A1:B49"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.69921875" customWidth="1"/>
-    <col min="2" max="2" width="65.69921875" customWidth="1"/>
+    <col min="1" max="1" width="24.75" customWidth="1"/>
+    <col min="2" max="2" width="65.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="B14" s="10"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B14" s="10"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="B18" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B15" s="1" t="s">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="B19" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B16" s="1" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B17" s="1" t="s">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B18" s="1" t="s">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B19" s="1" t="s">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B20" s="1" t="s">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B21" s="1" t="s">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B22" s="1" t="s">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="B26" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B23" s="1" t="s">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="B27" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B24" s="1" t="s">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B25" s="1" t="s">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B26" s="1" t="s">
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B27" s="1" t="s">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="B31" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B28" s="1" t="s">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="B32" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B29" s="1" t="s">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="B33" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B30" s="1" t="s">
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B31" s="1" t="s">
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="B35" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B32" s="1" t="s">
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+      <c r="B36" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B33" s="1" t="s">
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B34" s="1" t="s">
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B35" s="1" t="s">
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B36" s="1" t="s">
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="B40" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B37" s="1" t="s">
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B38" s="1" t="s">
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="10" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B45" s="10"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>1</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>2</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>3</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>4</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>

--- a/Form-Layout/ImportLayouts/Config/RPT_Import_Map.xlsx
+++ b/Form-Layout/ImportLayouts/Config/RPT_Import_Map.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\GitHub\SBO_Seoul\Form-Layout\ImportLayouts\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{574C74F8-808E-4F14-A9E2-6561A3BA2FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D77615D-4176-4487-9172-F8F4173A195A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{014D90F8-196E-40BF-BFE8-06F39FDF4BE1}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="522">
   <si>
     <t>No</t>
   </si>
@@ -1282,6 +1282,327 @@
   </si>
   <si>
     <t>ใบสั่งซื้อ (BP Catalog No.)</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>2. Sales - AR\1. Sales Quotation\1.Sale Quotation_ใบเสนอราคาขาย_(Dis)</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>149</t>
+  </si>
+  <si>
+    <t>Sales Quotation (Dis) v1 - SDA</t>
+  </si>
+  <si>
+    <t>รองรับส่วนลด (โฟลเดอร์ 1.)</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>1.Delivery_ใบส่งของ_(Batch_Serial).rpt</t>
+  </si>
+  <si>
+    <t>2. Sales - AR\3. Delivery\1.Delivery_ใบส่งของ_(Batch_Serial)</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>Delivery (B/S) v1 - SDA</t>
+  </si>
+  <si>
+    <t>Batch/Serial (โฟลเดอร์ 1.)</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>2. Sales - AR\4. Return\1.Retrun_ใบรับคืนสินค้า_(Batch_Serial)</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>Return (B/S) v1 - SDA</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>1.AR Down PaymentTax Invoice_ใบเสร็จรับเงินมัดจำใบกำกับภาษี.rpt</t>
+  </si>
+  <si>
+    <t>2. Sales - AR\5. AR Down Payment Invoice\1.AR Down PaymentTax Invoice_ใบเสร็จรับเงินมัดจำใบกำกับภาษี</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>65300</t>
+  </si>
+  <si>
+    <t>AR DP Tax v1 - SDA</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>1.AR Invoice_ใบแจ้งหนี้_(Dis).rpt</t>
+  </si>
+  <si>
+    <t>2. Sales - AR\6. AR Invoice\1.AR Invoice_ใบแจ้งหนี้_(Dis)</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>AR Invoice (Dis) v1 - SDA</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>1.AR_Credit Memo_ใบลดหนี้_(Dis) แก้ไขยอดเงิน.rpt</t>
+  </si>
+  <si>
+    <t>2. Sales - AR\7. AR Credit Memo\1.AR_Credit Memo_ใบลดหนี้_(Dis)</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>AR CM (Dis+Adj) v1 - SDA</t>
+  </si>
+  <si>
+    <t>ส่วนลด + แก้ไขยอดเงิน</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>1.Goods Reciept PO_TH_ใบรับสินค้า_(Batch_Serial).rpt</t>
+  </si>
+  <si>
+    <t>3. Purchasing - AP\4. Goods Receipt PO\1.Goods Receive PO_TH_ใบรับสินค้า_(Batch_Serial) - Copy</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>GRPO (B/S) v1 - SDA</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>1.Goods Return_TH_ใบส่งคืนสินค้า_(Batch_Serial).rpt</t>
+  </si>
+  <si>
+    <t>3. Purchasing - AP\5. Goods Return\1.Goods Return_EN_ใบส่งคืนสินค้า_(Batch_Serial)</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>Goods Return (B/S) v1 - SDA</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>1.AP Down Payment Invoice_ใบจ่ายเงินมัดจำใบกำกับภาษี.rpt</t>
+  </si>
+  <si>
+    <t>3. Purchasing - AP\6. AP Down Payment Invoice\1.AP Down Payment Invoice_ใบจ่ายเงินมัดจำ_ใบแจ้งหนี้</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>65301</t>
+  </si>
+  <si>
+    <t>AP DP Tax v1 - SDA</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>1.AP Invoice_ใบแจ้งหนี้_(Batch_Serial).rpt</t>
+  </si>
+  <si>
+    <t>3. Purchasing - AP\7. AP Invoice\1.AP Invoice_ใบแจ้งหนี้_(Batch_Serial)</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>AP Invoice (B/S) v1 - SDA</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>Tax Report</t>
+  </si>
+  <si>
+    <t>PD-PP30 - N_03.rpt</t>
+  </si>
+  <si>
+    <t>9.TST\SQL_TST</t>
+  </si>
+  <si>
+    <t>PP30 (VAT Return)</t>
+  </si>
+  <si>
+    <t>PP30 - SDA</t>
+  </si>
+  <si>
+    <t>รายงาน ภพ.30 (ไม่ใช่ layout)</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>PD-PP30-Detail - N_03.rpt</t>
+  </si>
+  <si>
+    <t>PP30 Detail</t>
+  </si>
+  <si>
+    <t>PP30 Detail - SDA</t>
+  </si>
+  <si>
+    <t>รายงาน ภพ.30 (รายละเอียด)</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>PD-VatTax.rpt</t>
+  </si>
+  <si>
+    <t>VAT Tax Report</t>
+  </si>
+  <si>
+    <t>VAT Tax - SDA</t>
+  </si>
+  <si>
+    <t>รายงานภาษีมูลค่าเพิ่ม</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>PD-Wht3 - N_03.rpt</t>
+  </si>
+  <si>
+    <t>WHT PND3</t>
+  </si>
+  <si>
+    <t>WHT PND3 - SDA</t>
+  </si>
+  <si>
+    <t>หนังสือรับรองหัก ณ ที่จ่าย ภ.ง.ด.3</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>PD-Wht3-Detail - N_03.rpt</t>
+  </si>
+  <si>
+    <t>WHT PND3 Detail</t>
+  </si>
+  <si>
+    <t>WHT PND3 Detail - SDA</t>
+  </si>
+  <si>
+    <t>ภ.ง.ด.3 (รายละเอียด)</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>PD-Wht03-50_-_N_03_New.rpt</t>
+  </si>
+  <si>
+    <t>WHT PND3 (50 Tawi)</t>
+  </si>
+  <si>
+    <t>WHT PND3 50Tawi - SDA</t>
+  </si>
+  <si>
+    <t>ภ.ง.ด.3 ใบแนบ 50 ทวิ</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>PD-Wht53 - N_03.rpt</t>
+  </si>
+  <si>
+    <t>WHT PND53</t>
+  </si>
+  <si>
+    <t>WHT PND53 - SDA</t>
+  </si>
+  <si>
+    <t>หนังสือรับรองหัก ณ ที่จ่าย ภ.ง.ด.53</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>PD-Wht53-Detail - N_03.rpt</t>
+  </si>
+  <si>
+    <t>WHT PND53 Detail</t>
+  </si>
+  <si>
+    <t>WHT PND53 Detail - SDA</t>
+  </si>
+  <si>
+    <t>ภ.ง.ด.53 (รายละเอียด)</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>PD-Wht53-50_-_N_03_New.rpt</t>
+  </si>
+  <si>
+    <t>WHT PND53 (50 Tawi)</t>
+  </si>
+  <si>
+    <t>WHT PND53 50Tawi - SDA</t>
+  </si>
+  <si>
+    <t>ภ.ง.ด.53 ใบแนบ 50 ทวิ</t>
   </si>
 </sst>
 </file>
@@ -1750,7 +2071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F62795C-81CC-4DF6-8643-8C6776741771}">
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.75" customWidth="1"/>
@@ -4282,6 +4603,671 @@
       </c>
       <c r="K72" t="s">
         <v>414</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A73" s="13" t="s">
+        <v>415</v>
+      </c>
+      <c r="B73" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>416</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F73" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G73" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H73" s="13" t="s">
+        <v>417</v>
+      </c>
+      <c r="I73" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="J73" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="K73" s="13" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A74" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>423</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F74" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G74" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H74" s="13" t="s">
+        <v>424</v>
+      </c>
+      <c r="I74" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="J74" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="K74" s="13" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A75" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="B75" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>429</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F75" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="G75" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H75" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="I75" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="J75" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="K75" s="13" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A76" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="B76" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>434</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="F76" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="G76" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="H76" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="I76" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="J76" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="K76" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A77" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="B77" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="D77" s="13" t="s">
+        <v>441</v>
+      </c>
+      <c r="E77" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F77" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G77" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H77" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="I77" s="13" t="s">
+        <v>443</v>
+      </c>
+      <c r="J77" s="13" t="s">
+        <v>444</v>
+      </c>
+      <c r="K77" s="13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A78" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="B78" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="D78" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="E78" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F78" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G78" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H78" s="13" t="s">
+        <v>448</v>
+      </c>
+      <c r="I78" s="13" t="s">
+        <v>449</v>
+      </c>
+      <c r="J78" s="13" t="s">
+        <v>450</v>
+      </c>
+      <c r="K78" s="13" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A79" s="13" t="s">
+        <v>452</v>
+      </c>
+      <c r="B79" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="D79" s="13" t="s">
+        <v>454</v>
+      </c>
+      <c r="E79" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F79" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="G79" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="H79" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="I79" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="J79" s="13" t="s">
+        <v>457</v>
+      </c>
+      <c r="K79" s="13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A80" s="13" t="s">
+        <v>458</v>
+      </c>
+      <c r="B80" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>459</v>
+      </c>
+      <c r="D80" s="13" t="s">
+        <v>460</v>
+      </c>
+      <c r="E80" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F80" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="G80" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="H80" s="13" t="s">
+        <v>461</v>
+      </c>
+      <c r="I80" s="13" t="s">
+        <v>462</v>
+      </c>
+      <c r="J80" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="K80" s="13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A81" s="13" t="s">
+        <v>464</v>
+      </c>
+      <c r="B81" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>465</v>
+      </c>
+      <c r="D81" s="13" t="s">
+        <v>466</v>
+      </c>
+      <c r="E81" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="F81" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="G81" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="H81" s="13" t="s">
+        <v>467</v>
+      </c>
+      <c r="I81" s="13" t="s">
+        <v>468</v>
+      </c>
+      <c r="J81" s="13" t="s">
+        <v>469</v>
+      </c>
+      <c r="K81" s="13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A82" s="13" t="s">
+        <v>470</v>
+      </c>
+      <c r="B82" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C82" s="13" t="s">
+        <v>471</v>
+      </c>
+      <c r="D82" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="E82" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="F82" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="G82" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="H82" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="I82" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="J82" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="K82" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A83" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="B83" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="D83" s="13" t="s">
+        <v>478</v>
+      </c>
+      <c r="E83" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="F83" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="G83" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="H83" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="I83" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="J83" s="13" t="s">
+        <v>480</v>
+      </c>
+      <c r="K83" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A84" s="13" t="s">
+        <v>482</v>
+      </c>
+      <c r="B84" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>483</v>
+      </c>
+      <c r="D84" s="13" t="s">
+        <v>478</v>
+      </c>
+      <c r="E84" s="13" t="s">
+        <v>484</v>
+      </c>
+      <c r="F84" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="G84" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="H84" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="I84" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="J84" s="13" t="s">
+        <v>485</v>
+      </c>
+      <c r="K84" s="13" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A85" s="13" t="s">
+        <v>487</v>
+      </c>
+      <c r="B85" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>488</v>
+      </c>
+      <c r="D85" s="13" t="s">
+        <v>478</v>
+      </c>
+      <c r="E85" s="13" t="s">
+        <v>489</v>
+      </c>
+      <c r="F85" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="G85" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="H85" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="I85" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="J85" s="13" t="s">
+        <v>490</v>
+      </c>
+      <c r="K85" s="13" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A86" s="13" t="s">
+        <v>492</v>
+      </c>
+      <c r="B86" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="C86" s="13" t="s">
+        <v>493</v>
+      </c>
+      <c r="D86" s="13" t="s">
+        <v>478</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>494</v>
+      </c>
+      <c r="F86" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="G86" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="H86" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="I86" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="J86" s="13" t="s">
+        <v>495</v>
+      </c>
+      <c r="K86" s="13" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A87" s="13" t="s">
+        <v>497</v>
+      </c>
+      <c r="B87" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="C87" s="13" t="s">
+        <v>498</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>478</v>
+      </c>
+      <c r="E87" s="13" t="s">
+        <v>499</v>
+      </c>
+      <c r="F87" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="G87" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="H87" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="I87" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="J87" s="13" t="s">
+        <v>500</v>
+      </c>
+      <c r="K87" s="13" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A88" s="13" t="s">
+        <v>502</v>
+      </c>
+      <c r="B88" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="C88" s="13" t="s">
+        <v>503</v>
+      </c>
+      <c r="D88" s="13" t="s">
+        <v>478</v>
+      </c>
+      <c r="E88" s="13" t="s">
+        <v>504</v>
+      </c>
+      <c r="F88" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="G88" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="H88" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="I88" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="J88" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="K88" s="13" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A89" s="13" t="s">
+        <v>507</v>
+      </c>
+      <c r="B89" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="C89" s="13" t="s">
+        <v>508</v>
+      </c>
+      <c r="D89" s="13" t="s">
+        <v>478</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>509</v>
+      </c>
+      <c r="F89" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="G89" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="H89" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="I89" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="J89" s="13" t="s">
+        <v>510</v>
+      </c>
+      <c r="K89" s="13" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A90" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="B90" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>513</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>478</v>
+      </c>
+      <c r="E90" s="13" t="s">
+        <v>514</v>
+      </c>
+      <c r="F90" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="G90" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="H90" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="I90" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="J90" s="13" t="s">
+        <v>515</v>
+      </c>
+      <c r="K90" s="13" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A91" s="13" t="s">
+        <v>517</v>
+      </c>
+      <c r="B91" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>518</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>478</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>519</v>
+      </c>
+      <c r="F91" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="G91" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="H91" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="I91" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="J91" s="13" t="s">
+        <v>520</v>
+      </c>
+      <c r="K91" s="13" t="s">
+        <v>521</v>
       </c>
     </row>
   </sheetData>

--- a/Form-Layout/ImportLayouts/Config/RPT_Import_Map.xlsx
+++ b/Form-Layout/ImportLayouts/Config/RPT_Import_Map.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SBO_Seoul\Form-Layout\ImportLayouts\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A626F78D-E0F1-4E5C-8FE9-E1E62FCC0A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E85B195-9298-4205-8706-5F7608C85795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1536" windowWidth="21600" windowHeight="11292" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RPT_MAP" sheetId="1" r:id="rId1"/>
@@ -1031,7 +1031,7 @@
     <t>Fixed Asset &amp; Tax (TST) reports have Object_Type "-" and are skipped by Import_SQL_Direct.ps1</t>
   </si>
   <si>
-    <t>2.Incoming Payments.rpt</t>
+    <t>2.Incoming Payments_ใบเสร็จรับเงินใบกำกับภาษี.rpt</t>
   </si>
 </sst>
 </file>
@@ -1401,13 +1401,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J49"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="58.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1439,7 +1439,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -1567,7 +1567,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>48</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>57</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -1663,7 +1663,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>75</v>
       </c>
@@ -1695,7 +1695,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>84</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>93</v>
       </c>
@@ -1759,7 +1759,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>102</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>106</v>
       </c>
@@ -1823,7 +1823,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>72</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -1887,7 +1887,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -1919,7 +1919,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>54</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -1983,7 +1983,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>138</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>145</v>
       </c>
@@ -2047,7 +2047,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>114</v>
       </c>
@@ -2079,7 +2079,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>122</v>
       </c>
@@ -2111,7 +2111,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>99</v>
       </c>
@@ -2143,7 +2143,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>161</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>194</v>
       </c>
@@ -2239,7 +2239,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>198</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>201</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>209</v>
       </c>
@@ -2335,7 +2335,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>218</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>17</v>
       </c>
@@ -2399,7 +2399,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>229</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>238</v>
       </c>
@@ -2463,7 +2463,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>242</v>
       </c>
@@ -2495,7 +2495,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>252</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>257</v>
       </c>
@@ -2559,7 +2559,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>262</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>269</v>
       </c>
@@ -2623,7 +2623,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>274</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>279</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>284</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>290</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>294</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>298</v>
       </c>
@@ -2815,7 +2815,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>302</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>306</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>169</v>
       </c>
@@ -2911,7 +2911,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>313</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>317</v>
       </c>
@@ -2983,9 +2983,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>321</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>323</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3033,7 +3033,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -3049,7 +3049,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -3057,7 +3057,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -3065,7 +3065,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>322</v>
       </c>
@@ -3089,7 +3089,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>334</v>
       </c>
